--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$184</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6105" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6138" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1031,8 +1031,22 @@
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this.resolve()}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn:tumorkonferenz</t>
+  </si>
+  <si>
+    <t>tumorkonferenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tumorkonferenz)
+</t>
   </si>
   <si>
     <t>Procedure.partOf</t>
@@ -2385,7 +2399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK183"/>
+  <dimension ref="A1:AK184"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.44921875" customWidth="true" bestFit="true"/>
@@ -8201,7 +8215,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>321</v>
       </c>
@@ -8276,16 +8290,14 @@
         <v>74</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>321</v>
@@ -8300,7 +8312,7 @@
         <v>95</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -8308,21 +8320,23 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -8334,16 +8348,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8393,7 +8407,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8405,7 +8419,7 @@
         <v>95</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>74</v>
@@ -8413,42 +8427,42 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>74</v>
+        <v>333</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>159</v>
+        <v>334</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>10</v>
+        <v>335</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8474,13 +8488,13 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>337</v>
+        <v>74</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -8498,62 +8512,62 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>340</v>
+        <v>74</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>10</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8579,13 +8593,13 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -8603,10 +8617,10 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>83</v>
@@ -8621,16 +8635,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>74</v>
+        <v>344</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8640,7 +8654,7 @@
         <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -8652,13 +8666,13 @@
         <v>212</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8687,10 +8701,10 @@
         <v>149</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -8708,7 +8722,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8726,12 +8740,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8745,24 +8759,26 @@
         <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>99</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>74</v>
@@ -8787,13 +8803,13 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>74</v>
+        <v>354</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -8811,7 +8827,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>101</v>
+        <v>350</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8820,10 +8836,10 @@
         <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>74</v>
@@ -8831,21 +8847,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8857,17 +8873,15 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -8904,31 +8918,31 @@
         <v>74</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>74</v>
@@ -8936,14 +8950,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8959,23 +8973,21 @@
         <v>74</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>355</v>
+        <v>105</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>356</v>
+        <v>106</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>74</v>
       </c>
@@ -9011,9 +9023,11 @@
         <v>74</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>74</v>
       </c>
@@ -9021,7 +9035,7 @@
         <v>110</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9033,22 +9047,20 @@
         <v>95</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>358</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
@@ -9057,10 +9069,10 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -9072,10 +9084,10 @@
         <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>226</v>
@@ -9091,7 +9103,7 @@
         <v>74</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>362</v>
+        <v>74</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>74</v>
@@ -9106,26 +9118,26 @@
         <v>74</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>363</v>
+        <v>74</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>228</v>
@@ -9146,14 +9158,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
@@ -9165,25 +9179,29 @@
         <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>74</v>
       </c>
@@ -9192,7 +9210,7 @@
         <v>74</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>74</v>
@@ -9207,13 +9225,11 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>74</v>
+        <v>367</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -9231,19 +9247,19 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>74</v>
@@ -9251,21 +9267,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -9277,17 +9293,15 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>74</v>
@@ -9324,78 +9338,76 @@
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9431,42 +9443,42 @@
         <v>74</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9474,13 +9486,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -9489,18 +9501,20 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>74</v>
       </c>
@@ -9548,7 +9562,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9566,12 +9580,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9579,13 +9593,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
@@ -9594,20 +9608,18 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>74</v>
       </c>
@@ -9655,7 +9667,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9673,12 +9685,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9686,13 +9698,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -9701,19 +9713,19 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>74</v>
@@ -9762,7 +9774,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9782,10 +9794,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9808,19 +9820,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>74</v>
@@ -9869,7 +9881,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9889,10 +9901,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9915,19 +9927,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>74</v>
@@ -9976,7 +9988,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9994,26 +10006,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>381</v>
+        <v>74</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -10022,19 +10034,19 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>63</v>
+        <v>270</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>382</v>
+        <v>271</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>383</v>
+        <v>272</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>384</v>
+        <v>273</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>74</v>
@@ -10059,13 +10071,13 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>385</v>
+        <v>74</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>386</v>
+        <v>74</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -10083,7 +10095,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>380</v>
+        <v>274</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10095,50 +10107,54 @@
         <v>95</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>387</v>
+        <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>74</v>
+        <v>385</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
       </c>
@@ -10162,13 +10178,13 @@
         <v>74</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>74</v>
+        <v>389</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>74</v>
+        <v>390</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -10186,7 +10202,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>101</v>
+        <v>384</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -10195,10 +10211,10 @@
         <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>74</v>
+        <v>391</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>74</v>
@@ -10206,21 +10222,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -10232,17 +10248,15 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>74</v>
@@ -10279,31 +10293,31 @@
         <v>74</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>74</v>
@@ -10311,46 +10325,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>355</v>
+        <v>105</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>356</v>
+        <v>106</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>74</v>
       </c>
@@ -10386,9 +10398,11 @@
         <v>74</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>74</v>
       </c>
@@ -10396,7 +10410,7 @@
         <v>110</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10408,7 +10422,7 @@
         <v>95</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>74</v>
@@ -10416,10 +10430,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10427,31 +10441,35 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>99</v>
+        <v>359</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>74</v>
       </c>
@@ -10487,31 +10505,29 @@
         <v>74</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>74</v>
@@ -10519,21 +10535,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -10545,17 +10561,15 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>74</v>
@@ -10592,31 +10606,31 @@
         <v>74</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>74</v>
@@ -10624,21 +10638,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -10647,23 +10661,21 @@
         <v>74</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>74</v>
       </c>
@@ -10699,31 +10711,31 @@
         <v>74</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>74</v>
@@ -10731,10 +10743,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10757,18 +10769,20 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>74</v>
       </c>
@@ -10816,7 +10830,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -10836,10 +10850,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10862,18 +10876,18 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>74</v>
       </c>
@@ -10921,7 +10935,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -10936,15 +10950,15 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>396</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10967,17 +10981,17 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>74</v>
@@ -11026,7 +11040,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -11041,15 +11055,15 @@
         <v>96</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>74</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11072,19 +11086,17 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>74</v>
@@ -11133,7 +11145,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
@@ -11151,16 +11163,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
@@ -11172,7 +11182,7 @@
         <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -11181,19 +11191,19 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>401</v>
+        <v>262</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>402</v>
+        <v>263</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>403</v>
+        <v>264</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>404</v>
+        <v>265</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>74</v>
@@ -11203,7 +11213,7 @@
         <v>74</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>405</v>
+        <v>74</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>74</v>
@@ -11218,11 +11228,13 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>406</v>
+        <v>74</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -11240,16 +11252,16 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>96</v>
@@ -11258,14 +11270,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>74</v>
       </c>
@@ -11277,25 +11291,29 @@
         <v>83</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>98</v>
+        <v>405</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>99</v>
+        <v>406</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>74</v>
       </c>
@@ -11304,7 +11322,7 @@
         <v>74</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>74</v>
@@ -11319,13 +11337,11 @@
         <v>74</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>74</v>
+        <v>410</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -11343,19 +11359,19 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>74</v>
@@ -11363,21 +11379,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>74</v>
@@ -11389,17 +11405,15 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>74</v>
@@ -11436,46 +11450,44 @@
         <v>74</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>103</v>
       </c>
@@ -11484,10 +11496,10 @@
         <v>75</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>74</v>
@@ -11496,13 +11508,13 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>411</v>
+        <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>412</v>
+        <v>105</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>107</v>
@@ -11543,16 +11555,16 @@
         <v>74</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>111</v>
@@ -11575,18 +11587,20 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="B88" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>83</v>
@@ -11598,29 +11612,27 @@
         <v>74</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>125</v>
+        <v>415</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>236</v>
+        <v>417</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>416</v>
+        <v>74</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>74</v>
@@ -11662,19 +11674,19 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>74</v>
@@ -11682,10 +11694,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11708,24 +11720,26 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>419</v>
+        <v>236</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>74</v>
+        <v>420</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>74</v>
@@ -11767,7 +11781,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11787,10 +11801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11813,20 +11827,18 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>250</v>
+        <v>423</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>74</v>
       </c>
@@ -11838,7 +11850,7 @@
         <v>74</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>422</v>
+        <v>74</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>74</v>
@@ -11874,7 +11886,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11886,18 +11898,18 @@
         <v>95</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>423</v>
+        <v>96</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>424</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11905,13 +11917,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>74</v>
@@ -11920,19 +11932,19 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>256</v>
+        <v>425</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>74</v>
@@ -11945,7 +11957,7 @@
         <v>74</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>74</v>
@@ -11981,7 +11993,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -11993,7 +12005,7 @@
         <v>95</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>96</v>
+        <v>427</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>74</v>
@@ -12001,10 +12013,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12027,19 +12039,19 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>74</v>
@@ -12088,7 +12100,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -12106,16 +12118,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
@@ -12127,7 +12137,7 @@
         <v>83</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>74</v>
@@ -12136,19 +12146,19 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>360</v>
+        <v>263</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>361</v>
+        <v>264</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>74</v>
@@ -12158,7 +12168,7 @@
         <v>74</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>362</v>
+        <v>74</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>74</v>
@@ -12173,11 +12183,13 @@
         <v>74</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>427</v>
+        <v>74</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>74</v>
@@ -12195,13 +12207,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>95</v>
@@ -12213,14 +12225,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
@@ -12232,25 +12246,29 @@
         <v>83</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>74</v>
       </c>
@@ -12259,7 +12277,7 @@
         <v>74</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>74</v>
@@ -12274,13 +12292,11 @@
         <v>74</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>74</v>
+        <v>431</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>74</v>
@@ -12298,19 +12314,19 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>74</v>
@@ -12318,21 +12334,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -12344,17 +12360,15 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>74</v>
@@ -12391,78 +12405,76 @@
         <v>74</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>74</v>
       </c>
@@ -12498,42 +12510,42 @@
         <v>74</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12541,13 +12553,13 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>74</v>
@@ -12556,18 +12568,20 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>74</v>
       </c>
@@ -12615,7 +12629,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -12633,12 +12647,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12646,13 +12660,13 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>74</v>
@@ -12661,20 +12675,18 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>74</v>
       </c>
@@ -12722,7 +12734,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -12740,12 +12752,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12753,13 +12765,13 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>74</v>
@@ -12768,19 +12780,19 @@
         <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>74</v>
@@ -12829,7 +12841,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -12849,10 +12861,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12875,19 +12887,19 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>74</v>
@@ -12936,7 +12948,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -12954,16 +12966,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
@@ -12975,7 +12985,7 @@
         <v>83</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>74</v>
@@ -12984,19 +12994,19 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>437</v>
+        <v>263</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>438</v>
+        <v>264</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>74</v>
@@ -13021,11 +13031,13 @@
         <v>74</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>439</v>
+        <v>74</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>74</v>
@@ -13043,13 +13055,13 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>95</v>
@@ -13061,14 +13073,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C102" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="B102" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
@@ -13080,25 +13094,29 @@
         <v>83</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>99</v>
+        <v>441</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>74</v>
       </c>
@@ -13122,13 +13140,11 @@
         <v>74</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>74</v>
+        <v>443</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>74</v>
@@ -13146,19 +13162,19 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>74</v>
@@ -13166,21 +13182,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>74</v>
@@ -13192,17 +13208,15 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>74</v>
@@ -13239,31 +13253,31 @@
         <v>74</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>74</v>
@@ -13271,21 +13285,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>74</v>
@@ -13294,23 +13308,21 @@
         <v>74</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>74</v>
       </c>
@@ -13346,31 +13358,31 @@
         <v>74</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>74</v>
@@ -13378,10 +13390,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13389,7 +13401,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>83</v>
@@ -13404,18 +13416,20 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>74</v>
       </c>
@@ -13463,7 +13477,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -13483,10 +13497,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13494,7 +13508,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>83</v>
@@ -13509,18 +13523,18 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>74</v>
       </c>
@@ -13568,7 +13582,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -13588,10 +13602,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13599,7 +13613,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>83</v>
@@ -13614,17 +13628,17 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>74</v>
@@ -13673,7 +13687,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -13693,10 +13707,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13719,19 +13733,17 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>74</v>
@@ -13780,7 +13792,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -13800,10 +13812,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13826,19 +13838,19 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>74</v>
@@ -13887,7 +13899,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -13896,7 +13908,7 @@
         <v>83</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>96</v>
@@ -13905,26 +13917,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>449</v>
+        <v>74</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>74</v>
@@ -13933,18 +13945,20 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>450</v>
+        <v>98</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>451</v>
+        <v>270</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>452</v>
+        <v>271</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>74</v>
       </c>
@@ -13992,10 +14006,10 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>448</v>
+        <v>274</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>83</v>
@@ -14004,7 +14018,7 @@
         <v>95</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>74</v>
@@ -14012,18 +14026,18 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>74</v>
+        <v>453</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>83</v>
@@ -14047,7 +14061,7 @@
         <v>456</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>457</v>
+        <v>326</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14097,10 +14111,10 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>83</v>
@@ -14109,18 +14123,18 @@
         <v>95</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14128,7 +14142,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>83</v>
@@ -14143,16 +14157,16 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14190,17 +14204,19 @@
         <v>74</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AC112" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>464</v>
+        <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
@@ -14212,7 +14228,7 @@
         <v>95</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>74</v>
@@ -14220,10 +14236,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14231,30 +14247,32 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>98</v>
+        <v>463</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>99</v>
+        <v>464</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>74</v>
@@ -14291,19 +14309,17 @@
         <v>74</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="AC113" s="2"/>
       <c r="AD113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>74</v>
+        <v>468</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>101</v>
+        <v>462</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14312,10 +14328,10 @@
         <v>83</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>74</v>
@@ -14323,21 +14339,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>74</v>
@@ -14349,17 +14365,15 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>74</v>
@@ -14396,31 +14410,31 @@
         <v>74</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>74</v>
@@ -14428,21 +14442,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>74</v>
@@ -14451,19 +14465,19 @@
         <v>74</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>468</v>
+        <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>469</v>
+        <v>105</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14501,42 +14515,42 @@
         <v>74</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>472</v>
+        <v>111</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>474</v>
+        <v>74</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14559,24 +14573,22 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q116" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
         <v>74</v>
       </c>
@@ -14620,7 +14632,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -14629,25 +14641,23 @@
         <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
@@ -14668,22 +14678,24 @@
         <v>84</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="R117" t="s" s="2">
         <v>74</v>
       </c>
@@ -14727,7 +14739,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
@@ -14736,13 +14748,13 @@
         <v>83</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>95</v>
+        <v>477</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>74</v>
+        <v>485</v>
       </c>
     </row>
     <row r="118" hidden="true">
@@ -14750,9 +14762,11 @@
         <v>486</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>74</v>
       </c>
@@ -14770,18 +14784,20 @@
         <v>74</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>98</v>
+        <v>463</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>74</v>
@@ -14830,7 +14846,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>101</v>
+        <v>462</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>75</v>
@@ -14839,10 +14855,10 @@
         <v>83</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>74</v>
@@ -14850,21 +14866,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>74</v>
@@ -14876,17 +14892,15 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>74</v>
@@ -14923,74 +14937,74 @@
         <v>74</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>468</v>
+        <v>104</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>490</v>
+        <v>106</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15028,31 +15042,31 @@
         <v>74</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>472</v>
+        <v>111</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>74</v>
@@ -15060,10 +15074,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15071,7 +15085,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>83</v>
@@ -15086,24 +15100,22 @@
         <v>84</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q121" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
         <v>74</v>
       </c>
@@ -15147,7 +15159,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
@@ -15156,7 +15168,7 @@
         <v>83</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>96</v>
@@ -15165,16 +15177,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
@@ -15186,7 +15196,7 @@
         <v>83</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>74</v>
@@ -15195,7 +15205,7 @@
         <v>84</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>496</v>
@@ -15204,13 +15214,15 @@
         <v>497</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q122" s="2"/>
+      <c r="Q122" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="R122" t="s" s="2">
         <v>74</v>
       </c>
@@ -15254,7 +15266,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
@@ -15263,7 +15275,7 @@
         <v>83</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>95</v>
+        <v>477</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>96</v>
@@ -15277,9 +15289,11 @@
         <v>498</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
@@ -15300,7 +15314,7 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>500</v>
@@ -15309,7 +15323,7 @@
         <v>501</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>326</v>
+        <v>466</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -15359,7 +15373,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -15371,7 +15385,7 @@
         <v>95</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>74</v>
@@ -15405,13 +15419,13 @@
         <v>84</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>326</v>
@@ -15476,7 +15490,7 @@
         <v>95</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>74</v>
@@ -15484,10 +15498,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15498,7 +15512,7 @@
         <v>75</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>74</v>
@@ -15510,7 +15524,7 @@
         <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>507</v>
@@ -15518,7 +15532,9 @@
       <c r="M125" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N125" s="2"/>
+      <c r="N125" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>74</v>
@@ -15567,19 +15583,19 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>74</v>
@@ -15601,7 +15617,7 @@
         <v>75</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>74</v>
@@ -15610,16 +15626,16 @@
         <v>74</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>98</v>
+        <v>510</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>99</v>
+        <v>511</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>100</v>
+        <v>512</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15670,19 +15686,19 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>101</v>
+        <v>509</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>74</v>
@@ -15690,21 +15706,21 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>74</v>
@@ -15716,17 +15732,15 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>74</v>
@@ -15763,31 +15777,31 @@
         <v>74</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>74</v>
@@ -15795,14 +15809,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>512</v>
+        <v>103</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -15815,26 +15829,24 @@
         <v>74</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>513</v>
+        <v>105</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O128" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>74</v>
       </c>
@@ -15870,19 +15882,19 @@
         <v>74</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>515</v>
+        <v>111</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -15902,33 +15914,33 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>74</v>
+        <v>516</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>517</v>
@@ -15937,10 +15949,10 @@
         <v>518</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>349</v>
+        <v>107</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>519</v>
+        <v>304</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>74</v>
@@ -15965,13 +15977,13 @@
         <v>74</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>520</v>
+        <v>74</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>521</v>
+        <v>74</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>74</v>
@@ -15989,19 +16001,19 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>74</v>
@@ -16009,10 +16021,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16020,7 +16032,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>83</v>
@@ -16035,19 +16047,19 @@
         <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>74</v>
@@ -16072,13 +16084,13 @@
         <v>74</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>74</v>
+        <v>524</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>74</v>
+        <v>525</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>74</v>
@@ -16096,10 +16108,10 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>83</v>
@@ -16108,7 +16120,7 @@
         <v>95</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>74</v>
@@ -16116,10 +16128,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16127,7 +16139,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>83</v>
@@ -16139,22 +16151,22 @@
         <v>74</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>74</v>
@@ -16203,10 +16215,10 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>83</v>
@@ -16215,7 +16227,7 @@
         <v>95</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>74</v>
@@ -16223,10 +16235,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16246,22 +16258,22 @@
         <v>74</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>74</v>
@@ -16310,7 +16322,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -16322,7 +16334,7 @@
         <v>95</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>74</v>
@@ -16330,10 +16342,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16344,7 +16356,7 @@
         <v>75</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>74</v>
@@ -16356,7 +16368,7 @@
         <v>84</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>212</v>
+        <v>537</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>538</v>
@@ -16365,9 +16377,11 @@
         <v>539</v>
       </c>
       <c r="N133" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O133" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>74</v>
       </c>
@@ -16391,13 +16405,13 @@
         <v>74</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>541</v>
+        <v>74</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>542</v>
+        <v>74</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>74</v>
@@ -16415,30 +16429,30 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16452,7 +16466,7 @@
         <v>76</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>74</v>
@@ -16461,16 +16475,16 @@
         <v>84</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16496,13 +16510,13 @@
         <v>74</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>74</v>
+        <v>545</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>74</v>
+        <v>546</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>74</v>
@@ -16520,7 +16534,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -16532,7 +16546,7 @@
         <v>95</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>74</v>
@@ -16540,10 +16554,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16566,7 +16580,7 @@
         <v>84</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>212</v>
+        <v>548</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>549</v>
@@ -16601,13 +16615,13 @@
         <v>74</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>552</v>
+        <v>74</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>553</v>
+        <v>74</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>74</v>
@@ -16625,7 +16639,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -16637,18 +16651,18 @@
         <v>95</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16659,27 +16673,29 @@
         <v>75</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>99</v>
+        <v>553</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>74</v>
@@ -16704,13 +16720,13 @@
         <v>74</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>74</v>
+        <v>556</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>74</v>
+        <v>557</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>74</v>
@@ -16728,19 +16744,19 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>101</v>
+        <v>552</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>74</v>
@@ -16748,21 +16764,21 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>74</v>
@@ -16774,17 +16790,15 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>74</v>
@@ -16821,31 +16835,31 @@
         <v>74</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>74</v>
@@ -16853,14 +16867,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -16870,29 +16884,27 @@
         <v>76</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>355</v>
+        <v>105</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>356</v>
+        <v>106</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>74</v>
       </c>
@@ -16928,9 +16940,11 @@
         <v>74</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AC138" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD138" t="s" s="2">
         <v>74</v>
       </c>
@@ -16938,7 +16952,7 @@
         <v>110</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>75</v>
@@ -16950,22 +16964,20 @@
         <v>95</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>74</v>
       </c>
@@ -16974,7 +16986,7 @@
         <v>75</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>84</v>
@@ -16989,10 +17001,10 @@
         <v>137</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>226</v>
@@ -17035,16 +17047,14 @@
         <v>74</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF139" t="s" s="2">
         <v>228</v>
@@ -17065,14 +17075,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B140" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="B140" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C140" s="2"/>
+      <c r="C140" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>74</v>
       </c>
@@ -17084,25 +17096,29 @@
         <v>83</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>74</v>
       </c>
@@ -17150,19 +17166,19 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>74</v>
@@ -17170,21 +17186,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>74</v>
@@ -17196,17 +17212,15 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>74</v>
@@ -17243,78 +17257,76 @@
         <v>74</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>74</v>
       </c>
@@ -17323,7 +17335,7 @@
         <v>74</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>566</v>
+        <v>74</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>74</v>
@@ -17350,31 +17362,31 @@
         <v>74</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>74</v>
@@ -17382,10 +17394,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17393,7 +17405,7 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>83</v>
@@ -17408,18 +17420,20 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O143" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>74</v>
       </c>
@@ -17428,7 +17442,7 @@
         <v>74</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>74</v>
+        <v>570</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>74</v>
@@ -17467,7 +17481,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>75</v>
@@ -17487,10 +17501,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17498,7 +17512,7 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>83</v>
@@ -17513,20 +17527,18 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>74</v>
       </c>
@@ -17574,7 +17586,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>75</v>
@@ -17592,12 +17604,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17605,13 +17617,13 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>74</v>
@@ -17620,19 +17632,19 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>74</v>
@@ -17681,7 +17693,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>75</v>
@@ -17701,10 +17713,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17727,19 +17739,19 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>74</v>
@@ -17788,7 +17800,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>75</v>
@@ -17808,10 +17820,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17834,19 +17846,19 @@
         <v>84</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>74</v>
@@ -17895,7 +17907,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>75</v>
@@ -17913,12 +17925,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17932,7 +17944,7 @@
         <v>83</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>74</v>
@@ -17941,18 +17953,20 @@
         <v>84</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>577</v>
+        <v>270</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>578</v>
+        <v>271</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>74</v>
       </c>
@@ -17976,11 +17990,13 @@
         <v>74</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y148" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z148" t="s" s="2">
-        <v>580</v>
+        <v>74</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -17998,7 +18014,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>576</v>
+        <v>274</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -18016,12 +18032,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18035,24 +18051,26 @@
         <v>83</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>99</v>
+        <v>581</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>74</v>
@@ -18077,13 +18095,11 @@
         <v>74</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>74</v>
+        <v>584</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>74</v>
@@ -18101,7 +18117,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>101</v>
+        <v>580</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>75</v>
@@ -18110,10 +18126,10 @@
         <v>83</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>74</v>
@@ -18121,21 +18137,21 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>74</v>
@@ -18147,17 +18163,15 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>74</v>
@@ -18194,31 +18208,31 @@
         <v>74</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>74</v>
@@ -18226,14 +18240,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18249,23 +18263,21 @@
         <v>74</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>584</v>
+        <v>105</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>585</v>
+        <v>106</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>74</v>
       </c>
@@ -18301,19 +18313,19 @@
         <v>74</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
@@ -18325,7 +18337,7 @@
         <v>74</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>74</v>
@@ -18333,10 +18345,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18347,7 +18359,7 @@
         <v>75</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>74</v>
@@ -18356,19 +18368,23 @@
         <v>74</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>99</v>
+        <v>588</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>74</v>
       </c>
@@ -18416,19 +18432,19 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>74</v>
@@ -18436,21 +18452,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>74</v>
@@ -18462,17 +18478,15 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>74</v>
@@ -18509,31 +18523,31 @@
         <v>74</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>74</v>
@@ -18541,21 +18555,21 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>74</v>
@@ -18564,23 +18578,21 @@
         <v>74</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>74</v>
       </c>
@@ -18589,7 +18601,7 @@
         <v>74</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>589</v>
+        <v>74</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>74</v>
@@ -18616,31 +18628,31 @@
         <v>74</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>74</v>
@@ -18648,10 +18660,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18674,18 +18686,20 @@
         <v>84</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>74</v>
       </c>
@@ -18694,7 +18708,7 @@
         <v>74</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>74</v>
+        <v>593</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>74</v>
@@ -18733,7 +18747,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>75</v>
@@ -18751,12 +18765,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18770,7 +18784,7 @@
         <v>83</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>74</v>
@@ -18779,18 +18793,18 @@
         <v>84</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>74</v>
       </c>
@@ -18838,7 +18852,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>75</v>
@@ -18853,15 +18867,15 @@
         <v>96</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>592</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18875,7 +18889,7 @@
         <v>83</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>74</v>
@@ -18884,17 +18898,17 @@
         <v>84</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>74</v>
@@ -18943,7 +18957,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -18958,15 +18972,15 @@
         <v>96</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>74</v>
+        <v>596</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18989,19 +19003,17 @@
         <v>84</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>74</v>
@@ -19050,7 +19062,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>75</v>
@@ -19070,10 +19082,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19096,19 +19108,19 @@
         <v>84</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>74</v>
@@ -19157,7 +19169,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -19177,10 +19189,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19191,7 +19203,7 @@
         <v>75</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>74</v>
@@ -19200,21 +19212,23 @@
         <v>74</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>597</v>
+        <v>98</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>598</v>
+        <v>270</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>599</v>
+        <v>271</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O160" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>74</v>
       </c>
@@ -19262,19 +19276,19 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>596</v>
+        <v>274</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>74</v>
@@ -19282,10 +19296,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19308,7 +19322,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>212</v>
+        <v>601</v>
       </c>
       <c r="L161" t="s" s="2">
         <v>602</v>
@@ -19343,13 +19357,13 @@
         <v>74</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>605</v>
+        <v>74</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>606</v>
+        <v>74</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>74</v>
@@ -19367,7 +19381,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>75</v>
@@ -19379,7 +19393,7 @@
         <v>95</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>74</v>
@@ -19387,10 +19401,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19413,20 +19427,18 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N162" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="L162" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>611</v>
-      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>74</v>
       </c>
@@ -19450,13 +19462,13 @@
         <v>74</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>74</v>
+        <v>609</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>74</v>
+        <v>610</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>74</v>
@@ -19474,7 +19486,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>75</v>
@@ -19486,7 +19498,7 @@
         <v>95</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>74</v>
@@ -19494,10 +19506,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19520,7 +19532,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>212</v>
+        <v>612</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>613</v>
@@ -19529,9 +19541,11 @@
         <v>614</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O163" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>74</v>
       </c>
@@ -19555,13 +19569,13 @@
         <v>74</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>615</v>
+        <v>74</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>616</v>
+        <v>74</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>74</v>
@@ -19579,7 +19593,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>75</v>
@@ -19591,18 +19605,18 @@
         <v>95</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19616,7 +19630,7 @@
         <v>76</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>74</v>
@@ -19625,16 +19639,16 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L164" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="N164" t="s" s="2">
-        <v>621</v>
+        <v>353</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -19660,13 +19674,13 @@
         <v>74</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>74</v>
+        <v>619</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>74</v>
+        <v>620</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>74</v>
@@ -19684,7 +19698,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>75</v>
@@ -19702,12 +19716,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19721,7 +19735,7 @@
         <v>76</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>74</v>
@@ -19730,7 +19744,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>506</v>
+        <v>622</v>
       </c>
       <c r="L165" t="s" s="2">
         <v>623</v>
@@ -19738,7 +19752,9 @@
       <c r="M165" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="N165" s="2"/>
+      <c r="N165" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>74</v>
@@ -19787,7 +19803,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>75</v>
@@ -19807,10 +19823,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19821,7 +19837,7 @@
         <v>75</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>74</v>
@@ -19833,13 +19849,13 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>98</v>
+        <v>510</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>99</v>
+        <v>627</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>100</v>
+        <v>628</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -19890,19 +19906,19 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>101</v>
+        <v>626</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>74</v>
@@ -19910,21 +19926,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>74</v>
@@ -19936,17 +19952,15 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>74</v>
@@ -19983,31 +19997,31 @@
         <v>74</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>74</v>
@@ -20015,14 +20029,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>512</v>
+        <v>103</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -20035,26 +20049,24 @@
         <v>74</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>513</v>
+        <v>105</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O168" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>74</v>
       </c>
@@ -20090,19 +20102,19 @@
         <v>74</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>515</v>
+        <v>111</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
@@ -20122,44 +20134,46 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>74</v>
+        <v>516</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>629</v>
+        <v>517</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>630</v>
+        <v>518</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O169" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>74</v>
       </c>
@@ -20183,13 +20197,13 @@
         <v>74</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>631</v>
+        <v>74</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>632</v>
+        <v>74</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>74</v>
@@ -20207,19 +20221,19 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>628</v>
+        <v>519</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>74</v>
@@ -20227,10 +20241,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20238,7 +20252,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>83</v>
@@ -20253,16 +20267,16 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L170" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>636</v>
-      </c>
       <c r="N170" t="s" s="2">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -20288,13 +20302,13 @@
         <v>74</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>74</v>
+        <v>635</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>74</v>
+        <v>636</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>74</v>
@@ -20312,10 +20326,10 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>83</v>
@@ -20324,7 +20338,7 @@
         <v>95</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>74</v>
@@ -20343,10 +20357,10 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>74</v>
@@ -20367,11 +20381,9 @@
         <v>640</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>74</v>
       </c>
@@ -20422,27 +20434,27 @@
         <v>637</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20456,7 +20468,7 @@
         <v>76</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>74</v>
@@ -20465,18 +20477,20 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>212</v>
+        <v>642</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N172" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O172" s="2"/>
+      <c r="O172" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>74</v>
       </c>
@@ -20500,11 +20514,13 @@
         <v>74</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="Y172" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z172" t="s" s="2">
-        <v>646</v>
+        <v>74</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>74</v>
@@ -20522,7 +20538,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -20534,13 +20550,13 @@
         <v>95</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>647</v>
       </c>
@@ -20556,10 +20572,10 @@
         <v>75</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>74</v>
@@ -20568,15 +20584,17 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>99</v>
+        <v>648</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N173" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>74</v>
@@ -20601,13 +20619,11 @@
         <v>74</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>74</v>
+        <v>650</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>74</v>
@@ -20625,19 +20641,19 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>101</v>
+        <v>647</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>74</v>
@@ -20645,21 +20661,21 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>74</v>
@@ -20671,17 +20687,15 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>74</v>
@@ -20718,31 +20732,31 @@
         <v>74</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>74</v>
@@ -20750,14 +20764,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -20773,23 +20787,21 @@
         <v>74</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>650</v>
+        <v>105</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>651</v>
+        <v>106</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>74</v>
       </c>
@@ -20825,19 +20837,19 @@
         <v>74</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
@@ -20849,7 +20861,7 @@
         <v>74</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>74</v>
@@ -20857,10 +20869,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20871,7 +20883,7 @@
         <v>75</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>74</v>
@@ -20880,19 +20892,23 @@
         <v>74</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>99</v>
+        <v>654</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>74</v>
       </c>
@@ -20940,19 +20956,19 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>74</v>
@@ -20960,21 +20976,21 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>74</v>
@@ -20986,17 +21002,15 @@
         <v>74</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>74</v>
@@ -21033,78 +21047,76 @@
         <v>74</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>74</v>
       </c>
@@ -21140,42 +21152,42 @@
         <v>74</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21183,13 +21195,13 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G179" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>74</v>
@@ -21198,18 +21210,20 @@
         <v>84</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O179" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>74</v>
       </c>
@@ -21257,7 +21271,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -21275,12 +21289,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21288,13 +21302,13 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>74</v>
@@ -21303,18 +21317,18 @@
         <v>84</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>74</v>
       </c>
@@ -21362,7 +21376,7 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
@@ -21377,15 +21391,15 @@
         <v>96</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>657</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21393,13 +21407,13 @@
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G181" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>74</v>
@@ -21408,17 +21422,17 @@
         <v>84</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>74</v>
@@ -21467,7 +21481,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>
@@ -21482,15 +21496,15 @@
         <v>96</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>74</v>
+        <v>661</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -21513,19 +21527,17 @@
         <v>84</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>74</v>
@@ -21574,7 +21586,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>75</v>
@@ -21594,10 +21606,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21620,19 +21632,19 @@
         <v>84</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>74</v>
@@ -21681,7 +21693,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>75</v>
@@ -21699,8 +21711,115 @@
         <v>74</v>
       </c>
     </row>
+    <row r="184" hidden="true">
+      <c r="A184" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G184" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="P184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q184" s="2"/>
+      <c r="R184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK184" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK183">
+  <autoFilter ref="A1:AK184">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21710,7 +21829,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI182">
+  <conditionalFormatting sqref="A2:AI183">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$223</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8021" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8061" uniqueCount="793">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1510,6 +1510,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -2132,6 +2135,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2769,7 +2788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN222"/>
+  <dimension ref="A1:AN223"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -5071,7 +5090,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>115</v>
@@ -5297,7 +5316,7 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
@@ -14405,7 +14424,7 @@
         <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>115</v>
@@ -14745,7 +14764,7 @@
         <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>115</v>
@@ -14969,7 +14988,7 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>99</v>
@@ -15195,7 +15214,7 @@
         <v>79</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>115</v>
@@ -15311,7 +15330,7 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>99</v>
@@ -15425,7 +15444,7 @@
         <v>87</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>99</v>
@@ -15479,7 +15498,9 @@
       <c r="M112" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N112" s="2"/>
+      <c r="N112" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O112" t="s" s="2">
         <v>246</v>
       </c>
@@ -15539,7 +15560,7 @@
         <v>87</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>99</v>
@@ -15559,10 +15580,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15593,7 +15614,9 @@
       <c r="M113" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N113" s="2"/>
+      <c r="N113" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O113" t="s" s="2">
         <v>253</v>
       </c>
@@ -15653,7 +15676,7 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>99</v>
@@ -15673,10 +15696,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15769,7 +15792,7 @@
         <v>87</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>99</v>
@@ -15789,7 +15812,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>442</v>
@@ -15818,7 +15841,7 @@
         <v>128</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>229</v>
@@ -15834,7 +15857,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>77</v>
@@ -15885,7 +15908,7 @@
         <v>87</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>99</v>
@@ -15905,7 +15928,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>443</v>
@@ -15934,10 +15957,10 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>239</v>
@@ -15999,7 +16022,7 @@
         <v>87</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>99</v>
@@ -16019,7 +16042,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>444</v>
@@ -16048,12 +16071,14 @@
         <v>162</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M117" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N117" s="2"/>
+      <c r="N117" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O117" t="s" s="2">
         <v>246</v>
       </c>
@@ -16068,7 +16093,7 @@
         <v>77</v>
       </c>
       <c r="T117" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="U117" t="s" s="2">
         <v>77</v>
@@ -16113,10 +16138,10 @@
         <v>87</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>77</v>
@@ -16133,7 +16158,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>446</v>
@@ -16167,7 +16192,9 @@
       <c r="M118" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N118" s="2"/>
+      <c r="N118" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O118" t="s" s="2">
         <v>253</v>
       </c>
@@ -16227,7 +16254,7 @@
         <v>87</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>99</v>
@@ -16247,7 +16274,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>447</v>
@@ -16343,7 +16370,7 @@
         <v>87</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>99</v>
@@ -16363,7 +16390,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>439</v>
@@ -16432,7 +16459,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>77</v>
@@ -16479,7 +16506,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>440</v>
@@ -16591,7 +16618,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>441</v>
@@ -16705,7 +16732,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>442</v>
@@ -16821,7 +16848,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>443</v>
@@ -16935,7 +16962,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>444</v>
@@ -17049,7 +17076,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>446</v>
@@ -17163,7 +17190,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>447</v>
@@ -17279,13 +17306,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>439</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>77</v>
@@ -17310,10 +17337,10 @@
         <v>140</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>283</v>
@@ -17348,7 +17375,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>77</v>
@@ -17395,7 +17422,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>440</v>
@@ -17507,7 +17534,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>441</v>
@@ -17621,7 +17648,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>442</v>
@@ -17737,7 +17764,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>443</v>
@@ -17851,7 +17878,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>444</v>
@@ -17965,7 +17992,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>446</v>
@@ -18079,7 +18106,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>447</v>
@@ -18195,10 +18222,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18311,14 +18338,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18337,13 +18364,13 @@
         <v>88</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18394,7 +18421,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>87</v>
@@ -18412,21 +18439,21 @@
         <v>77</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18535,10 +18562,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18649,10 +18676,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18678,13 +18705,13 @@
         <v>101</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18734,7 +18761,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18743,7 +18770,7 @@
         <v>87</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>99</v>
@@ -18763,10 +18790,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18792,13 +18819,13 @@
         <v>128</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -18827,10 +18854,10 @@
         <v>144</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>77</v>
@@ -18848,7 +18875,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18877,10 +18904,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18906,13 +18933,13 @@
         <v>343</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18962,7 +18989,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18991,10 +19018,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19020,13 +19047,13 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19076,7 +19103,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -19105,10 +19132,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19131,16 +19158,16 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19190,7 +19217,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19208,21 +19235,21 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19331,10 +19358,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19445,10 +19472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19474,13 +19501,13 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19530,7 +19557,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19539,7 +19566,7 @@
         <v>87</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19559,10 +19586,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19588,13 +19615,13 @@
         <v>128</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19623,10 +19650,10 @@
         <v>144</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>77</v>
@@ -19644,7 +19671,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19673,10 +19700,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19702,13 +19729,13 @@
         <v>343</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19758,7 +19785,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19787,10 +19814,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19816,13 +19843,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19872,7 +19899,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19901,10 +19928,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19927,16 +19954,16 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19974,17 +20001,17 @@
         <v>77</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -20002,21 +20029,21 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20125,10 +20152,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20239,10 +20266,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20268,13 +20295,13 @@
         <v>206</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -20324,7 +20351,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20333,13 +20360,13 @@
         <v>87</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>77</v>
@@ -20348,15 +20375,15 @@
         <v>77</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20382,20 +20409,20 @@
         <v>206</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q155" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R155" t="s" s="2">
         <v>77</v>
@@ -20440,7 +20467,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20449,13 +20476,13 @@
         <v>87</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>77</v>
@@ -20464,18 +20491,18 @@
         <v>77</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>77</v>
@@ -20497,16 +20524,16 @@
         <v>88</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20556,7 +20583,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20574,21 +20601,21 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20697,10 +20724,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20811,10 +20838,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20840,13 +20867,13 @@
         <v>206</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -20896,7 +20923,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20905,7 +20932,7 @@
         <v>87</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>99</v>
@@ -20920,15 +20947,15 @@
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20954,20 +20981,20 @@
         <v>206</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q160" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R160" t="s" s="2">
         <v>77</v>
@@ -21012,7 +21039,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -21021,7 +21048,7 @@
         <v>87</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>99</v>
@@ -21036,18 +21063,18 @@
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>77</v>
@@ -21072,13 +21099,13 @@
         <v>206</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21128,7 +21155,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21146,21 +21173,21 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21183,13 +21210,13 @@
         <v>88</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21240,7 +21267,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21261,7 +21288,7 @@
         <v>77</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>77</v>
@@ -21269,10 +21296,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21295,13 +21322,13 @@
         <v>88</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -21352,7 +21379,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21373,7 +21400,7 @@
         <v>77</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>77</v>
@@ -21381,10 +21408,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21407,13 +21434,13 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -21464,7 +21491,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21482,7 +21509,7 @@
         <v>77</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>77</v>
@@ -21493,10 +21520,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21605,10 +21632,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21719,14 +21746,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -21748,10 +21775,10 @@
         <v>107</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N167" t="s" s="2">
         <v>110</v>
@@ -21806,7 +21833,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21835,10 +21862,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21864,14 +21891,14 @@
         <v>275</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -21899,10 +21926,10 @@
         <v>152</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>77</v>
@@ -21920,7 +21947,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21938,21 +21965,21 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21975,17 +22002,17 @@
         <v>88</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -22034,7 +22061,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>87</v>
@@ -22052,21 +22079,21 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22089,17 +22116,17 @@
         <v>77</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -22148,7 +22175,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22177,10 +22204,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22203,17 +22230,17 @@
         <v>88</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22262,7 +22289,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22283,7 +22310,7 @@
         <v>77</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>77</v>
@@ -22291,10 +22318,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22320,13 +22347,13 @@
         <v>275</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22355,10 +22382,10 @@
         <v>152</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>77</v>
@@ -22376,7 +22403,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22394,10 +22421,10 @@
         <v>77</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>77</v>
@@ -22405,10 +22432,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22431,16 +22458,16 @@
         <v>88</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -22490,7 +22517,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22508,10 +22535,10 @@
         <v>77</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>77</v>
@@ -22519,10 +22546,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22548,13 +22575,13 @@
         <v>275</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -22583,10 +22610,10 @@
         <v>152</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>77</v>
@@ -22604,7 +22631,7 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -22628,15 +22655,15 @@
         <v>77</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22745,10 +22772,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22859,12 +22886,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="C177" s="2"/>
+      <c r="C177" t="s" s="2">
+        <v>684</v>
+      </c>
       <c r="D177" t="s" s="2">
         <v>77</v>
       </c>
@@ -22873,32 +22902,28 @@
         <v>78</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>140</v>
+        <v>685</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>402</v>
+        <v>686</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>77</v>
       </c>
@@ -22934,17 +22959,19 @@
         <v>77</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="AC177" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD177" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -22956,7 +22983,7 @@
         <v>77</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>77</v>
@@ -22968,19 +22995,17 @@
         <v>77</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>685</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>77</v>
       </c>
@@ -22989,7 +23014,7 @@
         <v>78</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>88</v>
@@ -23004,10 +23029,10 @@
         <v>140</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>283</v>
@@ -23050,16 +23075,14 @@
         <v>77</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF178" t="s" s="2">
         <v>285</v>
@@ -23089,14 +23112,16 @@
         <v>286</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="D179" t="s" s="2">
         <v>77</v>
       </c>
@@ -23108,25 +23133,29 @@
         <v>87</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>102</v>
+        <v>407</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
       </c>
@@ -23174,19 +23203,19 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>77</v>
@@ -23198,26 +23227,26 @@
         <v>77</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>77</v>
@@ -23229,17 +23258,15 @@
         <v>77</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -23276,31 +23303,31 @@
         <v>77</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>77</v>
@@ -23315,48 +23342,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>77</v>
       </c>
@@ -23365,7 +23390,7 @@
         <v>77</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>77</v>
@@ -23392,31 +23417,31 @@
         <v>77</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>77</v>
@@ -23428,15 +23453,15 @@
         <v>77</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23444,7 +23469,7 @@
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>87</v>
@@ -23459,18 +23484,20 @@
         <v>88</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O182" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>77</v>
       </c>
@@ -23479,7 +23506,7 @@
         <v>77</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>77</v>
@@ -23518,7 +23545,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -23542,15 +23569,15 @@
         <v>77</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23558,7 +23585,7 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>87</v>
@@ -23573,18 +23600,18 @@
         <v>88</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>77</v>
       </c>
@@ -23632,7 +23659,7 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>78</v>
@@ -23656,15 +23683,15 @@
         <v>77</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="184" hidden="true">
+    <row r="184">
       <c r="A184" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23672,13 +23699,13 @@
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I184" t="s" s="2">
         <v>77</v>
@@ -23687,17 +23714,17 @@
         <v>88</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
@@ -23746,7 +23773,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
@@ -23770,15 +23797,15 @@
         <v>77</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23801,19 +23828,17 @@
         <v>88</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>
@@ -23862,7 +23887,7 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23886,15 +23911,15 @@
         <v>77</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23917,19 +23942,19 @@
         <v>88</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -23978,7 +24003,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -24002,15 +24027,15 @@
         <v>77</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24024,7 +24049,7 @@
         <v>87</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>77</v>
@@ -24033,18 +24058,20 @@
         <v>88</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>275</v>
+        <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>702</v>
+        <v>305</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>703</v>
+        <v>306</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O187" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
       </c>
@@ -24068,11 +24095,13 @@
         <v>77</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y187" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z187" t="s" s="2">
-        <v>705</v>
+        <v>77</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>77</v>
@@ -24090,7 +24119,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>701</v>
+        <v>309</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -24114,15 +24143,15 @@
         <v>77</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
     </row>
-    <row r="188" hidden="true">
+    <row r="188">
       <c r="A188" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24136,24 +24165,26 @@
         <v>87</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>102</v>
+        <v>708</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N188" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>710</v>
+      </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>77</v>
@@ -24178,13 +24209,11 @@
         <v>77</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>77</v>
+        <v>711</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>77</v>
@@ -24202,7 +24231,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>104</v>
+        <v>707</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24214,7 +24243,7 @@
         <v>77</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>77</v>
@@ -24231,21 +24260,21 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>77</v>
@@ -24257,17 +24286,15 @@
         <v>77</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>77</v>
@@ -24304,31 +24331,31 @@
         <v>77</v>
       </c>
       <c r="AB189" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC189" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE189" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>77</v>
@@ -24345,14 +24372,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -24368,23 +24395,21 @@
         <v>77</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>709</v>
+        <v>108</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>710</v>
+        <v>109</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>77</v>
       </c>
@@ -24420,19 +24445,19 @@
         <v>77</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC190" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD190" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>78</v>
@@ -24444,7 +24469,7 @@
         <v>77</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>77</v>
@@ -24456,15 +24481,15 @@
         <v>77</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24475,7 +24500,7 @@
         <v>78</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>77</v>
@@ -24484,19 +24509,23 @@
         <v>77</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>102</v>
+        <v>715</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
+        <v>716</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P191" t="s" s="2">
         <v>77</v>
       </c>
@@ -24544,19 +24573,19 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>77</v>
@@ -24568,26 +24597,26 @@
         <v>77</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>77</v>
@@ -24599,17 +24628,15 @@
         <v>77</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>77</v>
@@ -24646,31 +24673,31 @@
         <v>77</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>77</v>
@@ -24687,21 +24714,21 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>77</v>
@@ -24710,23 +24737,21 @@
         <v>77</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>77</v>
       </c>
@@ -24735,7 +24760,7 @@
         <v>77</v>
       </c>
       <c r="S193" t="s" s="2">
-        <v>714</v>
+        <v>77</v>
       </c>
       <c r="T193" t="s" s="2">
         <v>77</v>
@@ -24762,31 +24787,31 @@
         <v>77</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>77</v>
@@ -24798,15 +24823,15 @@
         <v>77</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24829,18 +24854,20 @@
         <v>88</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O194" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>77</v>
       </c>
@@ -24849,7 +24876,7 @@
         <v>77</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>77</v>
+        <v>720</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>77</v>
@@ -24888,7 +24915,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -24912,15 +24939,15 @@
         <v>77</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24934,7 +24961,7 @@
         <v>87</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>77</v>
@@ -24943,18 +24970,18 @@
         <v>88</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N195" s="2"/>
-      <c r="O195" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>77</v>
       </c>
@@ -25002,7 +25029,7 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
@@ -25017,7 +25044,7 @@
         <v>99</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>717</v>
+        <v>77</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>77</v>
@@ -25026,15 +25053,15 @@
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="196" hidden="true">
+    <row r="196">
       <c r="A196" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25048,7 +25075,7 @@
         <v>87</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>77</v>
@@ -25057,17 +25084,17 @@
         <v>88</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>77</v>
@@ -25116,7 +25143,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25131,7 +25158,7 @@
         <v>99</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>77</v>
+        <v>723</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>77</v>
@@ -25140,15 +25167,15 @@
         <v>77</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25171,19 +25198,17 @@
         <v>88</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>77</v>
@@ -25232,7 +25257,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25256,15 +25281,15 @@
         <v>77</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25287,19 +25312,19 @@
         <v>88</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>77</v>
@@ -25348,7 +25373,7 @@
         <v>77</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>78</v>
@@ -25372,15 +25397,15 @@
         <v>77</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25391,7 +25416,7 @@
         <v>78</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>77</v>
@@ -25400,21 +25425,23 @@
         <v>77</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>722</v>
+        <v>101</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>723</v>
+        <v>305</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>724</v>
+        <v>306</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O199" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O199" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P199" t="s" s="2">
         <v>77</v>
       </c>
@@ -25462,13 +25489,13 @@
         <v>77</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>721</v>
+        <v>309</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>77</v>
@@ -25486,15 +25513,15 @@
         <v>77</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25517,16 +25544,16 @@
         <v>77</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>275</v>
+        <v>728</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -25552,13 +25579,13 @@
         <v>77</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>730</v>
+        <v>77</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>731</v>
+        <v>77</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>77</v>
@@ -25576,7 +25603,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25631,18 +25658,18 @@
         <v>77</v>
       </c>
       <c r="K201" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L201" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="L201" t="s" s="2">
+      <c r="M201" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="M201" t="s" s="2">
+      <c r="N201" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="N201" s="2"/>
-      <c r="O201" t="s" s="2">
-        <v>736</v>
-      </c>
+      <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>77</v>
       </c>
@@ -25666,13 +25693,13 @@
         <v>77</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>77</v>
+        <v>736</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>77</v>
+        <v>737</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>77</v>
@@ -25719,10 +25746,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25745,16 +25772,18 @@
         <v>77</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>275</v>
+        <v>739</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N202" s="2"/>
-      <c r="O202" s="2"/>
+      <c r="O202" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="P202" t="s" s="2">
         <v>77</v>
       </c>
@@ -25778,13 +25807,13 @@
         <v>77</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>740</v>
+        <v>77</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>741</v>
+        <v>77</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>77</v>
@@ -25802,7 +25831,7 @@
         <v>77</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
@@ -25829,12 +25858,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25848,7 +25877,7 @@
         <v>79</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>77</v>
@@ -25857,7 +25886,7 @@
         <v>77</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>743</v>
+        <v>275</v>
       </c>
       <c r="L203" t="s" s="2">
         <v>744</v>
@@ -25890,13 +25919,13 @@
         <v>77</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>77</v>
+        <v>746</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>77</v>
+        <v>747</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>77</v>
@@ -25914,7 +25943,7 @@
         <v>77</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>78</v>
@@ -25932,16 +25961,16 @@
         <v>77</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>746</v>
+        <v>77</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>747</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="204" hidden="true">
+    <row r="204">
       <c r="A204" t="s" s="2">
         <v>748</v>
       </c>
@@ -25960,7 +25989,7 @@
         <v>79</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>77</v>
@@ -25969,13 +25998,13 @@
         <v>77</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>621</v>
+        <v>749</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -26044,21 +26073,21 @@
         <v>77</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>77</v>
+        <v>752</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>77</v>
+        <v>753</v>
       </c>
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26069,7 +26098,7 @@
         <v>78</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>77</v>
@@ -26081,13 +26110,13 @@
         <v>77</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>101</v>
+        <v>622</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>102</v>
+        <v>755</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>103</v>
+        <v>756</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26138,19 +26167,19 @@
         <v>77</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>104</v>
+        <v>754</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK205" t="s" s="2">
         <v>77</v>
@@ -26167,21 +26196,21 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>77</v>
@@ -26193,17 +26222,15 @@
         <v>77</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>77</v>
@@ -26252,19 +26279,19 @@
         <v>77</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>77</v>
@@ -26281,14 +26308,14 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>628</v>
+        <v>106</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
@@ -26301,26 +26328,24 @@
         <v>77</v>
       </c>
       <c r="I207" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J207" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K207" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>629</v>
+        <v>108</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>630</v>
+        <v>109</v>
       </c>
       <c r="N207" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O207" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>77</v>
       </c>
@@ -26368,7 +26393,7 @@
         <v>77</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>631</v>
+        <v>114</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>78</v>
@@ -26397,42 +26422,46 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I208" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>275</v>
+        <v>107</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>755</v>
+        <v>630</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="N208" s="2"/>
-      <c r="O208" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P208" t="s" s="2">
         <v>77</v>
       </c>
@@ -26456,13 +26485,13 @@
         <v>77</v>
       </c>
       <c r="X208" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>757</v>
+        <v>77</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>758</v>
+        <v>77</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>77</v>
@@ -26480,19 +26509,19 @@
         <v>77</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>754</v>
+        <v>632</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI208" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>77</v>
@@ -26509,10 +26538,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -26520,7 +26549,7 @@
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G209" t="s" s="2">
         <v>87</v>
@@ -26535,7 +26564,7 @@
         <v>77</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>760</v>
+        <v>275</v>
       </c>
       <c r="L209" t="s" s="2">
         <v>761</v>
@@ -26568,13 +26597,13 @@
         <v>77</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>77</v>
+        <v>763</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>77</v>
+        <v>764</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>77</v>
@@ -26592,10 +26621,10 @@
         <v>77</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>87</v>
@@ -26621,10 +26650,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26632,10 +26661,10 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>77</v>
@@ -26647,20 +26676,16 @@
         <v>77</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="O210" t="s" s="2">
         <v>768</v>
       </c>
+      <c r="N210" s="2"/>
+      <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>77</v>
       </c>
@@ -26708,13 +26733,13 @@
         <v>77</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>77</v>
@@ -26735,7 +26760,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
         <v>769</v>
       </c>
@@ -26754,7 +26779,7 @@
         <v>79</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>77</v>
@@ -26763,18 +26788,20 @@
         <v>77</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>275</v>
+        <v>770</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="O211" s="2"/>
+        <v>773</v>
+      </c>
+      <c r="O211" t="s" s="2">
+        <v>774</v>
+      </c>
       <c r="P211" t="s" s="2">
         <v>77</v>
       </c>
@@ -26798,11 +26825,13 @@
         <v>77</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y211" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y211" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z211" t="s" s="2">
-        <v>772</v>
+        <v>77</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>77</v>
@@ -26847,12 +26876,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="212" hidden="true">
+    <row r="212">
       <c r="A212" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26863,10 +26892,10 @@
         <v>78</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H212" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I212" t="s" s="2">
         <v>77</v>
@@ -26875,15 +26904,17 @@
         <v>77</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>102</v>
+        <v>776</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>777</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>773</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>77</v>
@@ -26908,13 +26939,11 @@
         <v>77</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y212" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y212" s="2"/>
       <c r="Z212" t="s" s="2">
-        <v>77</v>
+        <v>778</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>77</v>
@@ -26932,19 +26961,19 @@
         <v>77</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>104</v>
+        <v>775</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>77</v>
@@ -26961,21 +26990,21 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>77</v>
@@ -26987,17 +27016,15 @@
         <v>77</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>77</v>
@@ -27034,31 +27061,31 @@
         <v>77</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC213" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD213" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>77</v>
@@ -27075,14 +27102,14 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
@@ -27098,23 +27125,21 @@
         <v>77</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>776</v>
+        <v>108</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>777</v>
+        <v>109</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>77</v>
       </c>
@@ -27150,19 +27175,19 @@
         <v>77</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>78</v>
@@ -27174,7 +27199,7 @@
         <v>77</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>77</v>
@@ -27186,15 +27211,15 @@
         <v>77</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -27205,7 +27230,7 @@
         <v>78</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>77</v>
@@ -27214,19 +27239,23 @@
         <v>77</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>102</v>
+        <v>782</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N215" s="2"/>
-      <c r="O215" s="2"/>
+        <v>783</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O215" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P215" t="s" s="2">
         <v>77</v>
       </c>
@@ -27274,19 +27303,19 @@
         <v>77</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>77</v>
@@ -27298,26 +27327,26 @@
         <v>77</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>77</v>
@@ -27329,17 +27358,15 @@
         <v>77</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N216" s="2"/>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>77</v>
@@ -27376,31 +27403,31 @@
         <v>77</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>77</v>
@@ -27415,48 +27442,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>77</v>
       </c>
@@ -27492,31 +27517,31 @@
         <v>77</v>
       </c>
       <c r="AB217" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC217" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD217" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE217" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI217" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>77</v>
@@ -27528,15 +27553,15 @@
         <v>77</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="218" hidden="true">
+    <row r="218">
       <c r="A218" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27544,13 +27569,13 @@
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G218" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H218" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I218" t="s" s="2">
         <v>77</v>
@@ -27559,18 +27584,20 @@
         <v>88</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O218" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O218" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P218" t="s" s="2">
         <v>77</v>
       </c>
@@ -27618,7 +27645,7 @@
         <v>77</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>78</v>
@@ -27642,15 +27669,15 @@
         <v>77</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -27658,13 +27685,13 @@
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G219" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>77</v>
@@ -27673,18 +27700,18 @@
         <v>88</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N219" s="2"/>
-      <c r="O219" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>77</v>
       </c>
@@ -27732,7 +27759,7 @@
         <v>77</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>78</v>
@@ -27747,7 +27774,7 @@
         <v>99</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>783</v>
+        <v>77</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>77</v>
@@ -27756,15 +27783,15 @@
         <v>77</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="220" hidden="true">
+    <row r="220">
       <c r="A220" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -27772,13 +27799,13 @@
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G220" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H220" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I220" t="s" s="2">
         <v>77</v>
@@ -27787,17 +27814,17 @@
         <v>88</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>77</v>
@@ -27846,7 +27873,7 @@
         <v>77</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>78</v>
@@ -27861,7 +27888,7 @@
         <v>99</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>77</v>
+        <v>789</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>77</v>
@@ -27870,15 +27897,15 @@
         <v>77</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -27901,19 +27928,17 @@
         <v>88</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>77</v>
@@ -27962,7 +27987,7 @@
         <v>77</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>78</v>
@@ -27986,15 +28011,15 @@
         <v>77</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28017,19 +28042,19 @@
         <v>88</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O222" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>77</v>
@@ -28078,7 +28103,7 @@
         <v>77</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>78</v>
@@ -28102,11 +28127,127 @@
         <v>77</v>
       </c>
       <c r="AN222" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="223" hidden="true">
+      <c r="A223" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G223" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J223" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K223" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L223" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M223" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q223" s="2"/>
+      <c r="R223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF223" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH223" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ223" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN223" t="s" s="2">
         <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN222">
+  <autoFilter ref="A1:AN223">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28116,7 +28257,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI221">
+  <conditionalFormatting sqref="A2:AI222">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-systemische-therapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
